--- a/results/publication/Tables.xlsx
+++ b/results/publication/Tables.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="143">
   <si>
     <t>Group</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>Top-5 panel + logistic regression (in-fold selection)</t>
+  </si>
+  <si>
+    <t>Top-5 panel, features adjusted for contamination index in-fold</t>
   </si>
   <si>
     <t>PLS-DA, 2 components (all non-exposure compounds)</t>
@@ -2283,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2332,13 +2335,13 @@
         <v>45</v>
       </c>
       <c r="F2">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="G2">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="H2">
-        <v>0.269</v>
+        <v>0.267</v>
       </c>
       <c r="I2">
         <v>0.001</v>
@@ -2361,16 +2364,16 @@
         <v>45</v>
       </c>
       <c r="F3">
-        <v>0.831</v>
+        <v>0.775</v>
       </c>
       <c r="G3">
-        <v>0.023</v>
+        <v>0.046</v>
       </c>
       <c r="H3">
-        <v>0.338</v>
+        <v>0.194</v>
       </c>
       <c r="I3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2378,57 +2381,57 @@
         <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F4">
-        <v>0.511</v>
+        <v>0.83</v>
       </c>
       <c r="G4">
-        <v>0.113</v>
+        <v>0.023</v>
       </c>
       <c r="H4">
-        <v>-0.424</v>
+        <v>0.337</v>
       </c>
       <c r="I4">
-        <v>0.467</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>0.454</v>
+        <v>0.857</v>
       </c>
       <c r="G5">
-        <v>0.058</v>
+        <v>0.036</v>
       </c>
       <c r="H5">
-        <v>-0.19</v>
+        <v>0.375</v>
       </c>
       <c r="I5">
-        <v>0.505</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2439,7 +2442,7 @@
         <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6">
         <v>29</v>
@@ -2448,16 +2451,16 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>0.858</v>
+        <v>0.634</v>
       </c>
       <c r="G6">
-        <v>0.036</v>
+        <v>0.073</v>
       </c>
       <c r="H6">
-        <v>0.375</v>
+        <v>-0.078</v>
       </c>
       <c r="I6">
-        <v>0.002</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2468,7 +2471,7 @@
         <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D7">
         <v>29</v>
@@ -2483,7 +2486,7 @@
         <v>0.034</v>
       </c>
       <c r="H7">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="I7">
         <v>0.011</v>
@@ -2506,16 +2509,16 @@
         <v>14</v>
       </c>
       <c r="F8">
-        <v>0.845</v>
+        <v>0.842</v>
       </c>
       <c r="G8">
         <v>0.047</v>
       </c>
       <c r="H8">
-        <v>0.325</v>
+        <v>0.323</v>
       </c>
       <c r="I8">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2535,45 +2538,45 @@
         <v>14</v>
       </c>
       <c r="F9">
-        <v>0.766</v>
+        <v>0.672</v>
       </c>
       <c r="G9">
-        <v>0.033</v>
+        <v>0.067</v>
       </c>
       <c r="H9">
-        <v>0.221</v>
+        <v>-0.008</v>
       </c>
       <c r="I9">
-        <v>0.026</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E10">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>0.714</v>
+        <v>0.766</v>
       </c>
       <c r="G10">
-        <v>0.058</v>
+        <v>0.033</v>
       </c>
       <c r="H10">
-        <v>0.046</v>
+        <v>0.22</v>
       </c>
       <c r="I10">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2584,7 +2587,7 @@
         <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11">
         <v>20</v>
@@ -2593,74 +2596,161 @@
         <v>45</v>
       </c>
       <c r="F11">
-        <v>0.784</v>
+        <v>0.537</v>
       </c>
       <c r="G11">
-        <v>0.036</v>
+        <v>0.061</v>
       </c>
       <c r="H11">
-        <v>0.231</v>
+        <v>-0.349</v>
       </c>
       <c r="I11">
-        <v>0.004</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
         <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D12">
         <v>20</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F12">
-        <v>0.77</v>
+        <v>0.736</v>
       </c>
       <c r="G12">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="H12">
-        <v>0.175</v>
+        <v>0.138</v>
       </c>
       <c r="I12">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B13" t="s">
         <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D13">
         <v>20</v>
       </c>
       <c r="E13">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>0.78</v>
+      </c>
+      <c r="G13">
+        <v>0.036</v>
+      </c>
+      <c r="H13">
+        <v>0.226</v>
+      </c>
+      <c r="I13">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
         <v>18</v>
       </c>
-      <c r="F13">
-        <v>0.775</v>
-      </c>
-      <c r="G13">
+      <c r="F14">
+        <v>0.623</v>
+      </c>
+      <c r="G14">
+        <v>0.055</v>
+      </c>
+      <c r="H14">
+        <v>-0.184</v>
+      </c>
+      <c r="I14">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>18</v>
+      </c>
+      <c r="F15">
+        <v>0.614</v>
+      </c>
+      <c r="G15">
+        <v>0.061</v>
+      </c>
+      <c r="H15">
+        <v>-0.042</v>
+      </c>
+      <c r="I15">
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>18</v>
+      </c>
+      <c r="F16">
+        <v>0.771</v>
+      </c>
+      <c r="G16">
         <v>0.045</v>
       </c>
-      <c r="H13">
-        <v>0.232</v>
-      </c>
-      <c r="I13">
-        <v>0.008999999999999999</v>
+      <c r="H16">
+        <v>0.225</v>
+      </c>
+      <c r="I16">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
